--- a/settings/sim_settings_2026-08-11.xlsx
+++ b/settings/sim_settings_2026-08-11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseluisramirezcolon/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A74078B-E8DE-1643-B840-E5049C855E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E26719-8C18-D147-8069-3A3F3BA67415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="820" windowWidth="28040" windowHeight="17200" xr2:uid="{DAAF6E19-12FB-494B-9ED1-38F39E50D62C}"/>
+    <workbookView xWindow="1360" yWindow="1800" windowWidth="28040" windowHeight="17200" activeTab="2" xr2:uid="{DAAF6E19-12FB-494B-9ED1-38F39E50D62C}"/>
   </bookViews>
   <sheets>
     <sheet name="wvar" sheetId="1" r:id="rId1"/>
@@ -247,9 +247,6 @@
     <t>[0 0.02]</t>
   </si>
   <si>
-    <t>./Amino.Acid.Database.Release.2026-07-20.xlsx</t>
-  </si>
-  <si>
     <t>HLG_MNDO_pH_7_eV</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>[0 2.0]</t>
+  </si>
+  <si>
+    <t>./data/Amino.Acid.Database.Release.2026-07-20.xlsx</t>
   </si>
 </sst>
 </file>
@@ -725,7 +725,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -814,7 +814,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
@@ -884,7 +884,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
@@ -898,7 +898,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -912,7 +912,7 @@
         <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
@@ -985,7 +985,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1074,7 +1074,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
@@ -1116,7 +1116,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
         <v>50</v>
@@ -1144,7 +1144,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
         <v>65</v>
@@ -1158,7 +1158,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
         <v>37</v>
@@ -1172,7 +1172,7 @@
         <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" t="s">
         <v>63</v>
@@ -1186,7 +1186,7 @@
         <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
         <v>39</v>
@@ -1245,7 +1245,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1334,7 +1334,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
